--- a/artfynd/A 4820-2026 artfynd.xlsx
+++ b/artfynd/A 4820-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54268082</v>
+        <v>175252</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåreholm, Ög</t>
+          <t>NO RÅDAÄNGEN (08H5a07), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600724.7966862455</v>
+        <v>600493</v>
       </c>
       <c r="R2" t="n">
-        <v>6479204.850361365</v>
+        <v>6478867</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>080750071 / CAL LUCI / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,19 +761,478 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>202279</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83304</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>311</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca phaeocephala</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO RÅDAÄNGEN (08H5a07), Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600493</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6478867</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rönö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>080750071 / CHA PHAE / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6741413</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79795</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>374</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gul dropplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cliostomum corrugatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO RÅDAÄNGEN (08H5a07), Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6478867</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rönö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>080750071 / CLI CORR / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>415959</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75341</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gammelekslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lecanographa amylacea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO RÅDAÄNGEN (08H5a07), Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600493</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6478867</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rönö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1998-06-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>080750071 / LEC AMYL / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54268082</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kåreholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600725</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6479205</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rönö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-05-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-05-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Jörgen Sundin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Jörgen Sundin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4820-2026 artfynd.xlsx
+++ b/artfynd/A 4820-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/175252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/202279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/415959</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,8 +1258,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54268082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>